--- a/data-files/hlookup.xlsx
+++ b/data-files/hlookup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spaul\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sures\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32BC42E-DC09-4328-AFC4-972E5843A805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5F6AFF-D0E0-4709-9E19-27608E331F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{029C5CF2-AAEA-4476-BAE8-75A4DA0AE536}"/>
+    <workbookView xWindow="2130" yWindow="0" windowWidth="29100" windowHeight="15585" xr2:uid="{029C5CF2-AAEA-4476-BAE8-75A4DA0AE536}"/>
   </bookViews>
   <sheets>
     <sheet name="dashboard" sheetId="3" r:id="rId1"/>
@@ -119,7 +119,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="20"/>
       <color theme="1"/>
@@ -127,16 +127,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -144,14 +163,184 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Accent5" xfId="1" builtinId="45"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -484,39 +673,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E45EB51-39D7-4B18-8869-B39074C5C61E}">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="26.25" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="24.42578125" defaultRowHeight="26.25" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="16384" width="24.42578125" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B1">
+      <c r="B2" s="2">
         <v>2009</v>
       </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="6"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B2">
+      <c r="B3" s="2">
         <v>2015</v>
       </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="6"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="5"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="6"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
+    <row r="5" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="7" t="s">
         <v>23</v>
       </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
